--- a/Cell survival results/Results 18 November.xlsx
+++ b/Cell survival results/Results 18 November.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29523"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="161" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DBB1CA6-C201-4937-8737-05E32FD8BCBB}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{040C6C8C-B16C-4183-8A6C-09C780B9D1AD}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,25 +39,25 @@
     <t>Count</t>
   </si>
   <si>
-    <t>Rad</t>
+    <t>Dose</t>
   </si>
   <si>
-    <t>Dose</t>
+    <t>Rad</t>
   </si>
   <si>
     <t>Triplicate</t>
   </si>
   <si>
+    <t>P</t>
+  </si>
+  <si>
     <t>Proton H</t>
   </si>
   <si>
-    <t>X</t>
+    <t>Proton L</t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Proton L</t>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -143,14 +143,14 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{37FAF783-73A6-4F94-BD92-3AC8939CC73A}" name="Table1" displayName="Table1" ref="A1:E34" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:E34" xr:uid="{37FAF783-73A6-4F94-BD92-3AC8939CC73A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E34">
-    <sortCondition ref="A1:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E28">
+    <sortCondition ref="A1:A28"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{18509FCF-A7F7-4E73-B9CE-3B558C5AE746}" name="Flask nr"/>
     <tableColumn id="2" xr3:uid="{56C9B4FB-D0B9-4FA4-B608-EB17CDCC45E5}" name="Count"/>
-    <tableColumn id="3" xr3:uid="{70944FB0-020A-49CF-A96E-C52A2DB16B1C}" name="Rad"/>
-    <tableColumn id="4" xr3:uid="{A78DFE64-61BF-437E-B935-6B0A7AA6DBBB}" name="Dose"/>
+    <tableColumn id="3" xr3:uid="{70944FB0-020A-49CF-A96E-C52A2DB16B1C}" name="Dose"/>
+    <tableColumn id="4" xr3:uid="{A78DFE64-61BF-437E-B935-6B0A7AA6DBBB}" name="Rad"/>
     <tableColumn id="5" xr3:uid="{C8E7309D-6343-4528-9629-8C6B4BA33825}" name="Triplicate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -503,16 +503,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>131</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>107</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -520,166 +520,166 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>186</v>
-      </c>
-      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>184</v>
-      </c>
-      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>120</v>
-      </c>
-      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
+        <v>237</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>131</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>166</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
+        <v>139</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
+        <v>114</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>161</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
+        <v>141</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>8</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12">
-        <v>112</v>
-      </c>
-      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
         <v>6</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -687,16 +687,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>94</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -704,66 +704,66 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14">
+        <v>158</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
         <v>8</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
         <v>8</v>
       </c>
       <c r="E17">
@@ -772,33 +772,33 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>165</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>117</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -806,16 +806,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
         <v>7</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -823,33 +823,33 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B22">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -857,16 +857,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B23">
-        <v>142</v>
-      </c>
-      <c r="C23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
+        <v>156</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -874,84 +874,84 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B24">
-        <v>155</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B25">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25">
+        <v>158</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
         <v>8</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B26">
-        <v>126</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B27">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28">
-        <v>178</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -959,16 +959,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B29">
-        <v>165</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -976,84 +976,84 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B31">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31">
+        <v>44</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
         <v>8</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>11</v>
-      </c>
-      <c r="C32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32">
+        <v>64</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
         <v>8</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B33">
+        <v>53</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
         <v>7</v>
       </c>
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
       </c>
       <c r="E34">
         <v>2</v>
